--- a/excel-files/TAGUIG_PATEROS/MAHARLIKA INTEGRATED SCHOOL.xlsx
+++ b/excel-files/TAGUIG_PATEROS/MAHARLIKA INTEGRATED SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF86923C-C8F0-459D-809F-CFF690492A2A}"/>
+  <xr:revisionPtr revIDLastSave="506" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA35362-E200-466F-9AA3-BCB2D24CD1EB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5618,8 +5618,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5634,7 +5634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13840,186 +13840,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
@@ -14037,8 +13857,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14056,7 +13876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -22657,186 +22477,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22854,8 +22494,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
